--- a/nr-doc-core-allergy-intolerance/ig/StructureDefinition-fr-core-allergy-intolerance.xlsx
+++ b/nr-doc-core-allergy-intolerance/ig/StructureDefinition-fr-core-allergy-intolerance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T09:32:19+00:00</t>
+    <t>2026-09-16T08:22:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-allergy-intolerance/ig/StructureDefinition-fr-core-allergy-intolerance.xlsx
+++ b/nr-doc-core-allergy-intolerance/ig/StructureDefinition-fr-core-allergy-intolerance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T08:22:23+00:00</t>
+    <t>2026-09-16T15:48:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -273,7 +273,7 @@
   </si>
   <si>
     <t>ait-1:AllergyIntolerance.clinicalStatus SHALL be present if verificationStatus is not entered-in-error. {verificationStatus.coding.where(system = 'http://terminology.hl7.org/CodeSystem/allergyintolerance-verification' and code = 'entered-in-error').exists() or clinicalStatus.exists()}
-ait-2:AllergyIntolerance.clinicalStatus SHALL NOT be present if verification Status is entered-in-error {verificationStatus.coding.where(system = 'http://terminology.hl7.org/CodeSystem/allergyintolerance-verification' and code = 'entered-in-error').empty() or clinicalStatus.empty()}dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+ait-2:AllergyIntolerance.clinicalStatus SHALL NOT be present if verification Status is entered-in-error {verificationStatus.coding.where(system = 'http://terminology.hl7.org/CodeSystem/allergyintolerance-verification' and code = 'entered-in-error').empty() or clinicalStatus.empty()}dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}fr-core-allergy-intolerance-1:Si type = allergie, les manifestations doivent être codées avec le ValueSet CIM-11 Chapitre 04, Bloc Affections allergiques ou d'hypersensibilité (fr-core-vs-allergyintolerance-manifestation-allergie). {type = 'allergy' implies reaction.manifestation.all(memberOf('https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-allergyintolerance-manifestation-allergie'))}fr-core-allergy-intolerance-2:Si type = hypersensibilité non allergique, les manifestations doivent être codées avec le ValueSet CIM-11 Chapitre 21 (fr-core-vs-allergyintolerance-manifestation-hypersensibilite). {type.extension('http://hl7.org/fhir/5.0/StructureDefinition/extension-AllergyIntolerance.type').value.coding.exists(system = 'http://snomed.info/sct' and code = '609396006') implies reaction.manifestation.all(memberOf('https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-allergyintolerance-manifestation-hypersensibilite'))}fr-core-allergy-intolerance-3:Si type = intolérance, les manifestations doivent être codées avec le ValueSet CIM-11 Chapitre 21 (fr-core-vs-allergyintolerance-manifestation-intolerance). {type = 'intolerance' implies reaction.manifestation.all(memberOf('https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-allergyintolerance-manifestation-intolerance'))}fr-core-allergy-intolerance-4:Si type = idiosyncrasie, les manifestations doivent être codées avec le ValueSet CIM-11 Chapitre 21 (fr-core-vs-allergyintolerance-manifestation-idiosyncrasie). {type.extension('http://hl7.org/fhir/5.0/StructureDefinition/extension-AllergyIntolerance.type').value.coding.exists(system = 'http://snomed.info/sct' and code = '56840009') implies reaction.manifestation.all(memberOf('https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-allergyintolerance-manifestation-idiosyncrasie'))}</t>
   </si>
   <si>
     <t>Observation[classCode=OBS, moodCode=EVN]</t>

--- a/nr-doc-core-allergy-intolerance/ig/StructureDefinition-fr-core-allergy-intolerance.xlsx
+++ b/nr-doc-core-allergy-intolerance/ig/StructureDefinition-fr-core-allergy-intolerance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T15:48:58+00:00</t>
+    <t>2026-09-17T13:27:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-allergy-intolerance/ig/StructureDefinition-fr-core-allergy-intolerance.xlsx
+++ b/nr-doc-core-allergy-intolerance/ig/StructureDefinition-fr-core-allergy-intolerance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T13:27:58+00:00</t>
+    <t>2026-10-13T15:20:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>FRCoreAllergyIntoleranceProfile est un profil utilisé pourdécrire une allergie ou une hypersensibilité non allergique ou une intolérance ou une idiosyncrasie.</t>
+    <t>FRCoreAllergyIntoleranceProfile est un profil utilisé pour décrire une allergie ou une hypersensibilité non allergique ou une intolérance ou une idiosyncrasie.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/nr-doc-core-allergy-intolerance/ig/StructureDefinition-fr-core-allergy-intolerance.xlsx
+++ b/nr-doc-core-allergy-intolerance/ig/StructureDefinition-fr-core-allergy-intolerance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T15:20:13+00:00</t>
+    <t>2026-10-13T15:41:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
